--- a/product family/MX64/MX64 1X6 CKT (31403)/BOM.xlsx
+++ b/product family/MX64/MX64 1X6 CKT (31403)/BOM.xlsx
@@ -531,10 +531,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
         <v>314036001</v>
@@ -567,10 +567,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H3" t="n">
         <v>314036001</v>
@@ -603,10 +603,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H4" t="n">
         <v>314036001</v>
@@ -623,10 +623,10 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H5" t="n">
         <v>314036001</v>
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H6" t="n">
         <v>314036001</v>
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H7" t="n">
         <v>314036001</v>
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H8" t="n">
         <v>314036002</v>
@@ -767,10 +767,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H9" t="n">
         <v>314036002</v>
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H10" t="n">
         <v>314036002</v>
@@ -823,10 +823,10 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H11" t="n">
         <v>314036002</v>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H12" t="n">
         <v>314036002</v>
@@ -895,10 +895,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H13" t="n">
         <v>314036002</v>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H14" t="n">
         <v>314036003</v>
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H15" t="n">
         <v>314036003</v>
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H16" t="n">
         <v>314036003</v>
@@ -1023,10 +1023,10 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H17" t="n">
         <v>314036003</v>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G18" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H18" t="n">
         <v>314036003</v>
@@ -1095,10 +1095,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G19" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H19" t="n">
         <v>314036003</v>
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H20" t="n">
         <v>314036004</v>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H21" t="n">
         <v>314036004</v>
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H22" t="n">
         <v>314036004</v>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G23" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H23" t="n">
         <v>314036004</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G24" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H24" t="n">
         <v>314036004</v>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H25" t="n">
         <v>314036004</v>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H26" t="n">
         <v>314036005</v>
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H27" t="n">
         <v>314036005</v>
@@ -1419,10 +1419,10 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H28" t="n">
         <v>314036005</v>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G29" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H29" t="n">
         <v>314036005</v>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G30" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H30" t="n">
         <v>314036005</v>
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G31" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H31" t="n">
         <v>314036005</v>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H32" t="n">
         <v>314036006</v>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H33" t="n">
         <v>314036006</v>
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G34" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H34" t="n">
         <v>314036006</v>
@@ -1671,10 +1671,10 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G35" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H35" t="n">
         <v>314036006</v>
@@ -1707,10 +1707,10 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G36" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H36" t="n">
         <v>314036006</v>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G37" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H37" t="n">
         <v>314036006</v>
@@ -1815,10 +1815,10 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H39" t="n">
         <v>314036100</v>
@@ -1851,10 +1851,10 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G40" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H40" t="n">
         <v>314036100</v>
@@ -1871,10 +1871,10 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G41" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H41" t="n">
         <v>314036100</v>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G42" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H42" t="n">
         <v>314036100</v>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G43" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H43" t="n">
         <v>314036100</v>
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H45" t="n">
         <v>314036110</v>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G46" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H46" t="n">
         <v>314036110</v>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G47" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H47" t="n">
         <v>314036110</v>
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G48" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H48" t="n">
         <v>314036110</v>
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G49" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H49" t="n">
         <v>314036110</v>
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H50" t="n">
         <v>314036200</v>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G51" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H51" t="n">
         <v>314036200</v>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G52" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H52" t="n">
         <v>314036200</v>
@@ -2287,10 +2287,10 @@
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G53" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H53" t="n">
         <v>314036200</v>
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G54" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H54" t="n">
         <v>314036200</v>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G55" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H55" t="n">
         <v>314036200</v>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H56" t="n">
         <v>314036210</v>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G57" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H57" t="n">
         <v>314036210</v>
@@ -2467,10 +2467,10 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G58" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H58" t="n">
         <v>314036210</v>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G59" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H59" t="n">
         <v>314036210</v>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G60" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H60" t="n">
         <v>314036210</v>
@@ -2575,10 +2575,10 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G61" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H61" t="n">
         <v>314036210</v>
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H62" t="n">
         <v>314036500</v>
@@ -2647,10 +2647,10 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G63" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H63" t="n">
         <v>314036500</v>
@@ -2683,10 +2683,10 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G64" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H64" t="n">
         <v>314036500</v>
@@ -2703,10 +2703,10 @@
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G65" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H65" t="n">
         <v>314036500</v>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G66" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H66" t="n">
         <v>314036500</v>
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G67" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H67" t="n">
         <v>314036500</v>
@@ -2811,10 +2811,10 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H68" t="n">
         <v>314036510</v>
@@ -2847,10 +2847,10 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G69" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H69" t="n">
         <v>314036510</v>
@@ -2883,10 +2883,10 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G70" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H70" t="n">
         <v>314036510</v>
@@ -2919,10 +2919,10 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G71" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H71" t="n">
         <v>314036510</v>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G72" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H72" t="n">
         <v>314036510</v>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G73" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H73" t="n">
         <v>314036510</v>
@@ -3027,10 +3027,10 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H74" t="n">
         <v>314036600</v>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G75" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H75" t="n">
         <v>314036600</v>
@@ -3099,10 +3099,10 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G76" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H76" t="n">
         <v>314036600</v>
@@ -3119,10 +3119,10 @@
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G77" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H77" t="n">
         <v>314036600</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G78" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H78" t="n">
         <v>314036600</v>
@@ -3191,10 +3191,10 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G79" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H79" t="n">
         <v>314036600</v>
@@ -3227,10 +3227,10 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H80" t="n">
         <v>314036610</v>
@@ -3263,10 +3263,10 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G81" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H81" t="n">
         <v>314036610</v>
@@ -3299,10 +3299,10 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G82" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H82" t="n">
         <v>314036610</v>
@@ -3335,10 +3335,10 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G83" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H83" t="n">
         <v>314036610</v>
@@ -3371,10 +3371,10 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G84" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H84" t="n">
         <v>314036610</v>
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G85" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H85" t="n">
         <v>314036610</v>
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H86" t="n">
         <v>314036700</v>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G87" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H87" t="n">
         <v>314036700</v>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G88" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H88" t="n">
         <v>314036700</v>
@@ -3535,10 +3535,10 @@
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G89" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H89" t="n">
         <v>314036700</v>
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G90" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H90" t="n">
         <v>314036700</v>
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G91" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H91" t="n">
         <v>314036700</v>
@@ -3643,10 +3643,10 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H92" t="n">
         <v>314036710</v>
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G93" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H93" t="n">
         <v>314036710</v>
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G94" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H94" t="n">
         <v>314036710</v>
@@ -3751,10 +3751,10 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G95" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H95" t="n">
         <v>314036710</v>
@@ -3787,10 +3787,10 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G96" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H96" t="n">
         <v>314036710</v>
@@ -3823,10 +3823,10 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G97" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H97" t="n">
         <v>314036710</v>
